--- a/execl/skill.xlsx
+++ b/execl/skill.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="677">
   <si>
     <t>技能表总览</t>
   </si>
@@ -97,10 +97,13 @@
     <t>枚举字典表</t>
   </si>
   <si>
-    <t>全表枚举值的中英文对照字典，供程序映射和策划查阅</t>
-  </si>
-  <si>
-    <t>填表规则</t>
+    <t>全表枚举值的中英文对照字典，先服务中文设计，定稿后再映射程序英文。</t>
+  </si>
+  <si>
+    <t>设计流程</t>
+  </si>
+  <si>
+    <t>设计阶段所有参数先写中文；设计定稿后补【名词备注表】；最后再统一替换为英文。</t>
   </si>
   <si>
     <t>1. ID命名规范</t>
@@ -136,7 +139,7 @@
     <t>6. 被动触发条件</t>
   </si>
   <si>
-    <t>使用表达式写法，如 HP&lt;30%、命中次数&gt;=10、目标拥有Buff=感电</t>
+    <t>使用表达式写法，如 HP&lt;30%、命中次数&gt;=10、目标拥有状态=感电</t>
   </si>
   <si>
     <t>7. 程序映射</t>
@@ -169,10 +172,10 @@
 闪电链=闪电链</t>
   </si>
   <si>
-    <t>技能标签；多个标签用 | 分隔，服务 build/装备/祝福联动。</t>
-  </si>
-  <si>
-    <t>伤害类型；填写程序枚举值，中文请查 skill_enum。</t>
+    <t>技能标签；多个标签用 | 分隔，服务流派/装备/祝福联动。</t>
+  </si>
+  <si>
+    <t>伤害类型；设计阶段先填写中文，定稿后再由名词备注表统一映射英文。</t>
   </si>
   <si>
     <t>参数包ID；关联 skill_param。</t>
@@ -400,7 +403,7 @@
     <t>param_pistol_01</t>
   </si>
   <si>
-    <t>调用参数：param_pistol_01；无额外触发；无附带buff。</t>
+    <t>调用参数：param_pistol_01；无额外触发；无附带状态。</t>
   </si>
   <si>
     <t>skill_006</t>
@@ -424,7 +427,7 @@
     <t>buff_machinegun_01</t>
   </si>
   <si>
-    <t>调用参数：param_machinegun_01；触发包：trigger_machinegun_01；buff包：buff_machinegun_01。</t>
+    <t>调用参数：param_machinegun_01；触发包：trigger_machinegun_01；状态包：buff_machinegun_01。</t>
   </si>
   <si>
     <t>skill_007</t>
@@ -454,7 +457,7 @@
     <t>buff_lasercannon_01</t>
   </si>
   <si>
-    <t>调用参数：param_lasercannon_01；无额外触发；buff包：buff_lasercannon_01。</t>
+    <t>调用参数：param_lasercannon_01；无额外触发；状态包：buff_lasercannon_01。</t>
   </si>
   <si>
     <t>skill_008</t>
@@ -475,7 +478,7 @@
     <t>trigger_beam_01</t>
   </si>
   <si>
-    <t>调用参数：param_beam_01；触发包：trigger_beam_01；无附带buff。</t>
+    <t>调用参数：param_beam_01；触发包：trigger_beam_01；无附带状态。</t>
   </si>
   <si>
     <t>skill_009</t>
@@ -493,7 +496,7 @@
     <t>buff_lightningchain_01</t>
   </si>
   <si>
-    <t>调用参数：param_lightningchain_01；触发包：trigger_lightningchain_01；buff包：buff_lightningchain_01。</t>
+    <t>调用参数：param_lightningchain_01；触发包：trigger_lightningchain_01；状态包：buff_lightningchain_01。</t>
   </si>
   <si>
     <t>skill_010</t>
@@ -517,7 +520,7 @@
     <t>buff_icebomb_01</t>
   </si>
   <si>
-    <t>调用参数：param_icebomb_01；触发包：trigger_icebomb_01；buff包：buff_icebomb_01。</t>
+    <t>调用参数：param_icebomb_01；触发包：trigger_icebomb_01；状态包：buff_icebomb_01。</t>
   </si>
   <si>
     <t>skill_011</t>
@@ -889,7 +892,7 @@
     <t>执行顺序；同一触发包内按从小到大执行。</t>
   </si>
   <si>
-    <t>触发事件；合法值请查 skill_enum。</t>
+    <t>触发事件；合法值请查 枚举字典表。</t>
   </si>
   <si>
     <t>触发条件；当前样例使用标准字符串，后续复杂后可拆条件表。</t>
@@ -952,7 +955,7 @@
     <t>maxTriggerCount</t>
   </si>
   <si>
-    <t>None</t>
+    <t>无</t>
   </si>
   <si>
     <t>无附带触发</t>
@@ -976,7 +979,7 @@
     <t>击杀时</t>
   </si>
   <si>
-    <t>目标拥有Buff=感电</t>
+    <t>目标拥有状态=感电</t>
   </si>
   <si>
     <t>最近敌人</t>
@@ -1045,7 +1048,7 @@
     <t>火焰炸弹结束飞行后在落点爆炸。</t>
   </si>
   <si>
-    <t>目标拥有Buff=点燃</t>
+    <t>目标拥有状态=点燃</t>
   </si>
   <si>
     <t>skill_A_106</t>
@@ -1225,7 +1228,7 @@
     <t>叠层规则；叠加=层数累加，刷新=重置计时，取最高=保留最高值。</t>
   </si>
   <si>
-    <t>被动标签；多个标签用 | 分隔，服务 build/装备/祝福联动。</t>
+    <t>被动标签；多个标签用 | 分隔，服务 流派/装备/祝福联动。</t>
   </si>
   <si>
     <t>被动ID</t>
@@ -1285,7 +1288,7 @@
     <t>暴击强化</t>
   </si>
   <si>
-    <t>暴击率提升15%，适配高暴击build。</t>
+    <t>暴击率提升15%，适配高暴击流派。</t>
   </si>
   <si>
     <t>装备</t>
@@ -1381,7 +1384,7 @@
     <t>冰霜|控制|装备</t>
   </si>
   <si>
-    <t>冰系build关键被动</t>
+    <t>冰系流派关键被动</t>
   </si>
   <si>
     <t>passive_005</t>
@@ -1657,7 +1660,7 @@
     <t>中文名</t>
   </si>
   <si>
-    <t>说明</t>
+    <t>说明（设计阶段优先看中文名）</t>
   </si>
   <si>
     <t>适用字段</t>
@@ -3356,63 +3359,63 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -3441,7 +3444,7 @@
   <sheetData>
     <row r="1" ht="16.5" customHeight="1" spans="1:12">
       <c r="A1" s="29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="29" t="s">
         <v>5</v>
@@ -3459,10 +3462,10 @@
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:12">
       <c r="A2" s="30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -3477,560 +3480,560 @@
     </row>
     <row r="3" ht="148.5" customHeight="1" spans="1:12">
       <c r="A3" s="26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" s="26"/>
       <c r="E3" s="26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" s="26"/>
       <c r="I3" s="26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L3" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:12">
       <c r="A4" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H4" s="27" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:12">
       <c r="A5" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J5" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:12">
       <c r="A6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="G6" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="28" t="s">
+      <c r="I6" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>72</v>
-      </c>
       <c r="J6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" ht="39" customHeight="1" spans="1:12">
       <c r="A7" s="31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" ht="33" customHeight="1" spans="1:12">
       <c r="A8" s="33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H8" s="33"/>
       <c r="I8" s="33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L8" s="34" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="33" customHeight="1" spans="1:12">
       <c r="A9" s="33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H9" s="33"/>
       <c r="I9" s="33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J9" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K9" s="33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L9" s="34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" ht="33" customHeight="1" spans="1:12">
       <c r="A10" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" s="33"/>
       <c r="I10" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J10" s="33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F11" s="35"/>
       <c r="G11" s="35"/>
       <c r="H11" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J11" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K11" s="35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L11" s="36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F12" s="35"/>
       <c r="G12" s="35"/>
       <c r="H12" s="35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J12" s="35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K12" s="35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L12" s="36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:12">
       <c r="A13" s="35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H13" s="35"/>
       <c r="I13" s="35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K13" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="35" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F14" s="35"/>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
       <c r="I14" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K14" s="35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B15" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" s="35" t="s">
-        <v>97</v>
-      </c>
       <c r="E15" s="35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F15" s="35"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
       <c r="I15" s="35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J15" s="35" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K15" s="35" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L15" s="35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:12">
       <c r="A16" s="35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C16" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="35" t="s">
-        <v>153</v>
-      </c>
       <c r="F16" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
       <c r="I16" s="35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J16" s="35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K16" s="35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L16" s="35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C17" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="35" t="s">
         <v>162</v>
-      </c>
-      <c r="D17" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="35" t="s">
-        <v>161</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
       <c r="I17" s="35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J17" s="35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K17" s="35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L17" s="35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F18" s="35"/>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
       <c r="I18" s="35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J18" s="35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K18" s="35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L18" s="35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4056,7 +4059,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>7</v>
@@ -4064,214 +4067,214 @@
     </row>
     <row r="2" ht="27" customHeight="1" spans="1:5">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" ht="82.5" customHeight="1" spans="1:5">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:5">
       <c r="A4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:5">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:5">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4292,10 +4295,10 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -4312,183 +4315,183 @@
     </row>
     <row r="2" ht="94.5" customHeight="1" spans="1:14">
       <c r="A2" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:14">
       <c r="A3" s="19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N3" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="40.5" customHeight="1" spans="1:14">
       <c r="A4" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N4" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" ht="40.5" customHeight="1" spans="1:14">
       <c r="A6" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="16">
         <v>600</v>
@@ -4500,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F6" s="16">
         <v>1</v>
@@ -4515,7 +4518,7 @@
         <v>10000</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K6" s="16">
         <v>1</v>
@@ -4527,12 +4530,12 @@
         <v>500</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1" spans="1:14">
       <c r="A7" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B7" s="16">
         <v>120</v>
@@ -4544,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F7" s="16">
         <v>1</v>
@@ -4559,7 +4562,7 @@
         <v>9000</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K7" s="16">
         <v>1</v>
@@ -4571,12 +4574,12 @@
         <v>450</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" ht="40.5" customHeight="1" spans="1:14">
       <c r="A8" s="22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="23">
         <v>700</v>
@@ -4588,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F8" s="23">
         <v>1</v>
@@ -4603,7 +4606,7 @@
         <v>10000</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K8" s="23">
         <v>3</v>
@@ -4615,12 +4618,12 @@
         <v>500</v>
       </c>
       <c r="N8" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" ht="40.5" customHeight="1" spans="1:14">
       <c r="A9" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="25">
         <v>1800</v>
@@ -4632,7 +4635,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F9" s="25">
         <v>1</v>
@@ -4647,7 +4650,7 @@
         <v>12000</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K9" s="25">
         <v>1</v>
@@ -4659,12 +4662,12 @@
         <v>550</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B10" s="3">
         <v>650</v>
@@ -4676,7 +4679,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -4691,7 +4694,7 @@
         <v>10000</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K10" s="3">
         <v>1</v>
@@ -4703,12 +4706,12 @@
         <v>520</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="3">
         <v>100</v>
@@ -4720,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
@@ -4735,7 +4738,7 @@
         <v>9000</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K11" s="3">
         <v>1</v>
@@ -4747,12 +4750,12 @@
         <v>480</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B12" s="3">
         <v>1500</v>
@@ -4764,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
@@ -4779,7 +4782,7 @@
         <v>11000</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K12" s="3">
         <v>99</v>
@@ -4791,12 +4794,12 @@
         <v>700</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B13" s="3">
         <v>3200</v>
@@ -4808,7 +4811,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
@@ -4823,7 +4826,7 @@
         <v>10000</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K13" s="3">
         <v>99</v>
@@ -4835,12 +4838,12 @@
         <v>600</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="3">
         <v>800</v>
@@ -4852,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
@@ -4867,7 +4870,7 @@
         <v>10000</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K14" s="3">
         <v>4</v>
@@ -4879,12 +4882,12 @@
         <v>520</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" s="3">
         <v>2200</v>
@@ -4896,7 +4899,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
@@ -4911,7 +4914,7 @@
         <v>11500</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K15" s="3">
         <v>1</v>
@@ -4923,12 +4926,12 @@
         <v>560</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B16" s="3">
         <v>2200</v>
@@ -4940,7 +4943,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
@@ -4955,7 +4958,7 @@
         <v>11500</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K16" s="3">
         <v>1</v>
@@ -4967,12 +4970,12 @@
         <v>560</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B17" s="3">
         <v>1900</v>
@@ -4984,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
@@ -4999,7 +5002,7 @@
         <v>12000</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K17" s="3">
         <v>1</v>
@@ -5011,7 +5014,7 @@
         <v>600</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5031,10 +5034,10 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -5046,138 +5049,138 @@
     </row>
     <row r="2" ht="108" customHeight="1" spans="1:9">
       <c r="A2" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:9">
       <c r="A3" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="40.5" customHeight="1" spans="1:9">
       <c r="A4" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>72</v>
-      </c>
       <c r="E5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>72</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1" spans="1:9">
       <c r="A6" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G6" s="16">
         <v>0</v>
@@ -5186,27 +5189,27 @@
         <v>0</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:9">
       <c r="A7" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G7" s="16">
         <v>0</v>
@@ -5215,27 +5218,27 @@
         <v>999</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" ht="40.5" customHeight="1" spans="1:9">
       <c r="A8" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G8" s="16">
         <v>0</v>
@@ -5244,27 +5247,27 @@
         <v>3</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1" spans="1:9">
       <c r="A9" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" s="16">
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G9" s="16">
         <v>0</v>
@@ -5273,27 +5276,27 @@
         <v>1</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1" spans="1:9">
       <c r="A10" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" s="16">
         <v>2</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G10" s="16">
         <v>150</v>
@@ -5302,27 +5305,27 @@
         <v>1</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -5331,27 +5334,27 @@
         <v>999</v>
       </c>
       <c r="I11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F12" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -5360,27 +5363,27 @@
         <v>6</v>
       </c>
       <c r="I12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F13" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -5389,27 +5392,27 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F14" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -5418,27 +5421,27 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -5447,27 +5450,27 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -5476,27 +5479,27 @@
         <v>2</v>
       </c>
       <c r="I16" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D17" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E17" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -5505,27 +5508,27 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D18" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G18">
         <v>150</v>
@@ -5534,7 +5537,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -5554,10 +5557,10 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -5569,135 +5572,135 @@
     </row>
     <row r="2" ht="81" customHeight="1" spans="1:9">
       <c r="A2" s="12" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" ht="27" customHeight="1" spans="1:9">
       <c r="A3" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:9">
       <c r="A4" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="F5" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>73</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" ht="27" customHeight="1" spans="1:9">
       <c r="A6" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F6" s="16">
         <v>0</v>
@@ -5709,24 +5712,24 @@
         <v>0</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" ht="40.5" customHeight="1" spans="1:9">
       <c r="A7" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B7" s="16">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F7" s="16">
         <v>1800</v>
@@ -5738,24 +5741,24 @@
         <v>2500</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" ht="40.5" customHeight="1" spans="1:9">
       <c r="A8" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B8" s="16">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F8" s="16">
         <v>3500</v>
@@ -5767,24 +5770,24 @@
         <v>3000</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" ht="27" customHeight="1" spans="1:9">
       <c r="A9" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="16">
         <v>2</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F9" s="16">
         <v>2000</v>
@@ -5796,24 +5799,24 @@
         <v>2000</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" ht="40.5" customHeight="1" spans="1:9">
       <c r="A10" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="16">
         <v>1</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F10" s="16">
         <v>5000</v>
@@ -5825,24 +5828,24 @@
         <v>4000</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F11">
         <v>3000</v>
@@ -5854,24 +5857,24 @@
         <v>2500</v>
       </c>
       <c r="I11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F12">
         <v>1500</v>
@@ -5883,24 +5886,24 @@
         <v>2200</v>
       </c>
       <c r="I12" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F13">
         <v>4000</v>
@@ -5912,24 +5915,24 @@
         <v>3200</v>
       </c>
       <c r="I13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F14">
         <v>2000</v>
@@ -5941,24 +5944,24 @@
         <v>2000</v>
       </c>
       <c r="I14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F15">
         <v>4500</v>
@@ -5970,24 +5973,24 @@
         <v>2200</v>
       </c>
       <c r="I15" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F16">
         <v>10000</v>
@@ -5999,24 +6002,24 @@
         <v>4000</v>
       </c>
       <c r="I16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E17" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F17">
         <v>6500</v>
@@ -6028,24 +6031,24 @@
         <v>4200</v>
       </c>
       <c r="I17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D18" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E18" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F18">
         <v>5000</v>
@@ -6057,7 +6060,7 @@
         <v>4000</v>
       </c>
       <c r="I18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -6083,7 +6086,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>15</v>
@@ -6104,219 +6107,219 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="104" customHeight="1" spans="1:15">
       <c r="A2" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" spans="1:15">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:15">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="M5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:15">
       <c r="A6" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>2</v>
@@ -6331,39 +6334,39 @@
         <v>2</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:15">
       <c r="A7" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>2</v>
@@ -6375,42 +6378,42 @@
         <v>99</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>2</v>
@@ -6422,42 +6425,42 @@
         <v>1</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>2</v>
@@ -6472,42 +6475,42 @@
         <v>2</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K10" s="3">
         <v>3000</v>
@@ -6519,39 +6522,39 @@
         <v>2</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>2</v>
@@ -6566,39 +6569,39 @@
         <v>2</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>2</v>
@@ -6613,42 +6616,42 @@
         <v>2</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K13" s="3">
         <v>0</v>
@@ -6657,13 +6660,13 @@
         <v>3</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -6680,7 +6683,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>17</v>
@@ -6688,162 +6691,162 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I5" t="s">
+        <v>262</v>
+      </c>
+      <c r="J5" t="s">
         <v>73</v>
       </c>
-      <c r="E5" t="s">
+      <c r="K5" t="s">
         <v>73</v>
-      </c>
-      <c r="F5" t="s">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s">
-        <v>261</v>
-      </c>
-      <c r="H5" t="s">
-        <v>261</v>
-      </c>
-      <c r="I5" t="s">
-        <v>261</v>
-      </c>
-      <c r="J5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6">
         <v>8000</v>
@@ -6855,30 +6858,30 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G7">
         <v>6000</v>
@@ -6890,30 +6893,30 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G8">
         <v>15000</v>
@@ -6925,30 +6928,30 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>2</v>
       </c>
       <c r="F9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G9">
         <v>12000</v>
@@ -6960,30 +6963,30 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10">
         <v>8000</v>
@@ -6995,30 +6998,30 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E11" t="s">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11">
         <v>6000</v>
@@ -7030,30 +7033,30 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G12">
         <v>6000</v>
@@ -7065,30 +7068,30 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F13" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G13">
         <v>12000</v>
@@ -7100,30 +7103,30 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K13" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G14">
         <v>12000</v>
@@ -7135,30 +7138,30 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C15" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G15">
         <v>8000</v>
@@ -7170,30 +7173,30 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K15" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B16" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C16" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G16">
         <v>15000</v>
@@ -7205,30 +7208,30 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K16" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B17" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C17" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G17">
         <v>12000</v>
@@ -7240,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K17" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -7260,1073 +7263,1073 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" t="s">
+        <v>546</v>
+      </c>
+      <c r="E3" t="s">
         <v>544</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" t="s">
-        <v>545</v>
-      </c>
-      <c r="E3" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
+        <v>554</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>555</v>
+      </c>
+      <c r="E7" t="s">
         <v>553</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>554</v>
-      </c>
-      <c r="E7" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E12" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
+        <v>571</v>
+      </c>
+      <c r="C15" t="s">
+        <v>501</v>
+      </c>
+      <c r="D15" t="s">
+        <v>572</v>
+      </c>
+      <c r="E15" t="s">
         <v>570</v>
-      </c>
-      <c r="C15" t="s">
-        <v>500</v>
-      </c>
-      <c r="D15" t="s">
-        <v>571</v>
-      </c>
-      <c r="E15" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C16" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D16" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E16" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C17" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D17" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E17" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C18" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D18" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E18" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
+        <v>580</v>
+      </c>
+      <c r="E19" t="s">
         <v>579</v>
-      </c>
-      <c r="E19" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E20" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E21" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C22" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D22" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E22" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D23" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C24" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D24" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E24" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C25" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D25" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E25" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C26" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D26" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E26" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C27" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D27" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E27" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C28" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D28" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E28" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E29" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C30" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D30" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E30" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C31" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D31" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E31" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C32" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D32" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E32" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C33" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D33" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E33" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B34" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C34" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D34" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E34" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B35" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C35" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D35" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E35" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C36" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D36" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E36" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D37" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E37" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C38" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D38" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E38" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C39" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D39" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E39" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B40" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C40" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D40" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E40" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s">
+        <v>629</v>
+      </c>
+      <c r="C41" t="s">
+        <v>367</v>
+      </c>
+      <c r="D41" t="s">
+        <v>630</v>
+      </c>
+      <c r="E41" t="s">
         <v>628</v>
-      </c>
-      <c r="C41" t="s">
-        <v>366</v>
-      </c>
-      <c r="D41" t="s">
-        <v>629</v>
-      </c>
-      <c r="E41" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C42" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D42" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E42" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s">
+        <v>634</v>
+      </c>
+      <c r="C43" t="s">
+        <v>317</v>
+      </c>
+      <c r="D43" t="s">
+        <v>635</v>
+      </c>
+      <c r="E43" t="s">
         <v>633</v>
-      </c>
-      <c r="C43" t="s">
-        <v>316</v>
-      </c>
-      <c r="D43" t="s">
-        <v>634</v>
-      </c>
-      <c r="E43" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B44" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D44" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E44" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B45" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C45" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D45" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E45" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B46" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C46" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D46" t="s">
+        <v>640</v>
+      </c>
+      <c r="E46" t="s">
         <v>639</v>
-      </c>
-      <c r="E46" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B47" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D47" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E47" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B48" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C48" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D48" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E48" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B49" t="s">
+        <v>647</v>
+      </c>
+      <c r="C49" t="s">
+        <v>318</v>
+      </c>
+      <c r="D49" t="s">
+        <v>648</v>
+      </c>
+      <c r="E49" t="s">
         <v>646</v>
-      </c>
-      <c r="C49" t="s">
-        <v>317</v>
-      </c>
-      <c r="D49" t="s">
-        <v>647</v>
-      </c>
-      <c r="E49" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B50" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C50" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D50" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E50" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B51" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C51" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D51" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E51" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B52" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D52" t="s">
+        <v>656</v>
+      </c>
+      <c r="E52" t="s">
         <v>655</v>
-      </c>
-      <c r="E52" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B53" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C53" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D53" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E53" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B54" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C54" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D54" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E54" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B55" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C55" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D55" t="s">
+        <v>663</v>
+      </c>
+      <c r="E55" t="s">
         <v>662</v>
-      </c>
-      <c r="E55" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B56" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C56" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D56" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E56" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B57" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C57" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D57" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E57" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B58" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C58" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D58" t="s">
+        <v>668</v>
+      </c>
+      <c r="E58" t="s">
         <v>667</v>
-      </c>
-      <c r="E58" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B59" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C59" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D59" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E59" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B60" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C60" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D60" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E60" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C61" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D61" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E61" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s">
+        <v>673</v>
+      </c>
+      <c r="C62" t="s">
+        <v>673</v>
+      </c>
+      <c r="D62" t="s">
+        <v>674</v>
+      </c>
+      <c r="E62" t="s">
         <v>672</v>
-      </c>
-      <c r="C62" t="s">
-        <v>672</v>
-      </c>
-      <c r="D62" t="s">
-        <v>673</v>
-      </c>
-      <c r="E62" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B63" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C63" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D63" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E63" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
   </sheetData>
